--- a/book/RISCV_Exercise/riscv_template_v4.xlsx
+++ b/book/RISCV_Exercise/riscv_template_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usafa0-my.sharepoint.com/personal/george_york_afacademy_af_edu/Documents/DocumentsOneDrive/ECE485/MIPS-RISCV Exercise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{21D500E5-5BC4-4577-8B1B-1D72002C6BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19949722-4745-4D02-BF6E-FA30602ADE07}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{21D500E5-5BC4-4577-8B1B-1D72002C6BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00BA073-B535-41A1-8AF0-0F10D1C461B8}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="with stalls and no forwarding" sheetId="1" r:id="rId1"/>
@@ -70,9 +70,6 @@
     <t>Code fixed with forwarding and branch fix (like Figure C.25)</t>
   </si>
   <si>
-    <t>Code fixed with Stalls and no forwarding (like figure C.18)</t>
-  </si>
-  <si>
     <t>Code fixed with forwarding and branch fix and instruction reordering (like Figure C.25)</t>
   </si>
   <si>
@@ -119,6 +116,9 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>Code fixed with Stalls and no forwarding (like figure C.18/C.19)</t>
   </si>
 </sst>
 </file>
@@ -538,7 +538,7 @@
   <sheetData>
     <row r="1" spans="1:198" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>6</v>
@@ -1332,10 +1332,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>1</v>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -1421,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -1431,10 +1431,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:198" x14ac:dyDescent="0.4">
@@ -1443,10 +1443,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="2"/>
     </row>
@@ -1456,10 +1456,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:198" x14ac:dyDescent="0.4">
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:198" x14ac:dyDescent="0.4">
@@ -1486,7 +1486,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:198" x14ac:dyDescent="0.4">
@@ -1495,10 +1495,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:198" x14ac:dyDescent="0.4">
@@ -1507,10 +1507,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:198" x14ac:dyDescent="0.4">
@@ -1519,10 +1519,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:198" x14ac:dyDescent="0.4">
@@ -1534,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
@@ -1558,10 +1558,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
@@ -1570,10 +1570,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
@@ -1582,10 +1582,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
@@ -1597,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
@@ -1612,7 +1612,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -1623,10 +1623,10 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" s="1"/>
     </row>
@@ -1636,10 +1636,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G24" s="2"/>
     </row>
@@ -1649,10 +1649,10 @@
         <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2"/>
     </row>
@@ -1680,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
@@ -1689,10 +1689,10 @@
         <v>26</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
@@ -1701,10 +1701,10 @@
         <v>27</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
@@ -1713,10 +1713,10 @@
         <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
@@ -1728,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
@@ -1743,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.4">
@@ -1752,10 +1752,10 @@
         <v>31</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.4">
@@ -1764,10 +1764,10 @@
         <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.4">
@@ -1776,10 +1776,10 @@
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="14.25" x14ac:dyDescent="0.4">
@@ -1791,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q36" s="6"/>
     </row>
@@ -1807,7 +1807,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q37" s="6"/>
     </row>
@@ -1817,10 +1817,10 @@
         <v>36</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q38" s="6"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>37</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q39" s="6"/>
     </row>
@@ -1843,10 +1843,10 @@
         <v>38</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="6"/>
     </row>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q41" s="6"/>
     </row>
@@ -1875,7 +1875,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q42" s="6"/>
     </row>
@@ -1885,10 +1885,10 @@
         <v>41</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q43" s="6"/>
     </row>
@@ -1898,10 +1898,10 @@
         <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q44" s="6"/>
     </row>
@@ -1911,10 +1911,10 @@
         <v>43</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q45" s="6"/>
     </row>
@@ -1927,10 +1927,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q46" s="6"/>
     </row>
@@ -1943,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q47" s="6"/>
     </row>
@@ -1953,10 +1953,10 @@
         <v>46</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q48" s="6"/>
     </row>
@@ -1966,10 +1966,10 @@
         <v>47</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q49" s="6"/>
     </row>
@@ -1979,10 +1979,10 @@
         <v>48</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q50" s="6"/>
     </row>
@@ -1992,13 +1992,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2467,10 +2467,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
@@ -2497,7 +2497,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>1</v>
@@ -2524,7 +2524,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
@@ -2540,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -2566,10 +2566,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.4">
@@ -2578,10 +2578,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="2"/>
     </row>
@@ -2591,10 +2591,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:109" x14ac:dyDescent="0.4">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:109" x14ac:dyDescent="0.4">
@@ -2621,7 +2621,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:109" x14ac:dyDescent="0.4">
@@ -2630,10 +2630,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:109" x14ac:dyDescent="0.4">
@@ -2642,10 +2642,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:109" x14ac:dyDescent="0.4">
@@ -2654,10 +2654,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:109" x14ac:dyDescent="0.4">
@@ -2669,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
@@ -2684,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
@@ -2693,10 +2693,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
@@ -2705,10 +2705,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
@@ -2717,10 +2717,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
@@ -2747,7 +2747,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2"/>
     </row>
@@ -2758,10 +2758,10 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" s="1"/>
     </row>
@@ -2771,10 +2771,10 @@
         <v>22</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G24" s="2"/>
     </row>
@@ -2784,10 +2784,10 @@
         <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2"/>
     </row>
@@ -2815,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
@@ -2824,10 +2824,10 @@
         <v>26</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
@@ -2836,10 +2836,10 @@
         <v>27</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
@@ -2848,10 +2848,10 @@
         <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
@@ -2863,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.4">
@@ -2887,10 +2887,10 @@
         <v>31</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.4">
@@ -2899,10 +2899,10 @@
         <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.4">
@@ -2911,10 +2911,10 @@
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="14.25" x14ac:dyDescent="0.4">
@@ -2926,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q36" s="6"/>
     </row>
@@ -2942,7 +2942,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q37" s="6"/>
     </row>
@@ -2952,10 +2952,10 @@
         <v>36</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q38" s="6"/>
     </row>
@@ -2965,10 +2965,10 @@
         <v>37</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q39" s="6"/>
     </row>
@@ -2978,10 +2978,10 @@
         <v>38</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="6"/>
     </row>
@@ -2994,10 +2994,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q41" s="6"/>
     </row>
@@ -3010,7 +3010,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q42" s="6"/>
     </row>
@@ -3020,10 +3020,10 @@
         <v>41</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q43" s="6"/>
     </row>
@@ -3033,10 +3033,10 @@
         <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q44" s="6"/>
     </row>
@@ -3046,10 +3046,10 @@
         <v>43</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q45" s="6"/>
     </row>
@@ -3062,10 +3062,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q46" s="6"/>
     </row>
@@ -3078,7 +3078,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q47" s="6"/>
     </row>
@@ -3088,10 +3088,10 @@
         <v>46</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q48" s="6"/>
     </row>
@@ -3101,10 +3101,10 @@
         <v>47</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q49" s="6"/>
     </row>
@@ -3114,10 +3114,10 @@
         <v>48</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q50" s="6"/>
     </row>
@@ -3127,13 +3127,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3155,7 +3155,7 @@
   <sheetData>
     <row r="1" spans="1:97" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3606,10 +3606,10 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
@@ -3690,7 +3690,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
@@ -3771,7 +3771,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2"/>
@@ -3843,10 +3843,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
